--- a/frontend/public/Mandi_Master_V10.xlsx
+++ b/frontend/public/Mandi_Master_V10.xlsx
@@ -13741,7 +13741,7 @@
         </is>
       </c>
       <c r="J5" s="12">
-        <f>SUMIFS(G:G,H:H,"CASH",D:D,"PAYMENT")+SUMIFS(G:G,H:H,"CASH",D:D,"MOTOR")+SUMIFS(G:G,H:H,"CASH",D:D,"BHUSSA")+SUMIFS(G:G,H:H,"CASH",D:D,"GAWALI")+SUMIFS(G:G,H:H,"CASH",D:D,"CASH_ADV")+SUMIFS(G:G,H:H,"CASH",D:D,"DISCOUNT")+SUMIFS(G:G,H:H,"CASH",D:D,"WITHDRAWN")+SUMIFS(G:G,H:H,"CASH",D:D,"REPAID")+SUMIFS(G:G,H:H,"CASH",D:D,"GIVEN")+SUMIFS(G:G,H:H,"CASH",D:D,"MANDI")+SUMIFS(G:G,H:H,"CASH",D:D,"TRAVEL")+SUMIFS(G:G,H:H,"CASH",D:D,"FOOD")+SUMIFS(G:G,H:H,"CASH",D:D,"SALARY")+SUMIFS(G:G,H:H,"CASH",D:D,"BF_DISC")+SUMIFS(G:G,H:H,"CASH",D:D,"JB_PAID")+SUMIFS(G:G,H:H,"CASH",D:D,"JB_WITHDRAW")+SUMIFS(G:G,H:H,"CASH",D:D,"KK_WITHDRAW")+SUMIFS(G:G,H:H,"CASH",D:D,"COMM_WITHDRAW")+SUMIFS(G:G,H:H,"CASH",D:D,"PROFIT_WITHDRAW")+SUMIFS(G:G,H:H,"CASH",D:D,"PAID")+SUMIFS(G:G,H:H,"CASH",D:D,"MISC")+SUMIFS(G:G,H:H,"CASH",D:D,"OTHER")+SUMIFS(G:G,H:H,"CASH",D:D,"MHN_PERSONAL")+SUMIFS(G:G,H:H,"CASH",D:D,"ADJUSTED")+SUMIFS(G:G,H:H,"CASH",D:D,"PROFIT_TO_CAP")</f>
+        <f>SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"PAYMENT")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"MOTOR")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"BHUSSA")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"GAWALI")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"CASH_ADV")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"DISCOUNT")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"WITHDRAWN")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"REPAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"GIVEN")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"MANDI")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"TRAVEL")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"FOOD")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"SALARY")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"BF_DISC")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"JB_PAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"JB_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"KK_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"COMM_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"PROFIT_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"PAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"MISC")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"OTHER")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"MHN_PERSONAL")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"ADJUSTED")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"PROFIT_TO_CAP")</f>
         <v/>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>SUMIFS(G:G,H:H,"BANK",D:D,"PAYMENT")+SUMIFS(G:G,H:H,"BANK",D:D,"MOTOR")+SUMIFS(G:G,H:H,"BANK",D:D,"BHUSSA")+SUMIFS(G:G,H:H,"BANK",D:D,"GAWALI")+SUMIFS(G:G,H:H,"BANK",D:D,"CASH_ADV")+SUMIFS(G:G,H:H,"BANK",D:D,"DISCOUNT")+SUMIFS(G:G,H:H,"BANK",D:D,"WITHDRAWN")+SUMIFS(G:G,H:H,"BANK",D:D,"REPAID")+SUMIFS(G:G,H:H,"BANK",D:D,"GIVEN")+SUMIFS(G:G,H:H,"BANK",D:D,"MANDI")+SUMIFS(G:G,H:H,"BANK",D:D,"TRAVEL")+SUMIFS(G:G,H:H,"BANK",D:D,"FOOD")+SUMIFS(G:G,H:H,"BANK",D:D,"SALARY")+SUMIFS(G:G,H:H,"BANK",D:D,"BF_DISC")+SUMIFS(G:G,H:H,"BANK",D:D,"JB_PAID")+SUMIFS(G:G,H:H,"BANK",D:D,"JB_WITHDRAW")+SUMIFS(G:G,H:H,"BANK",D:D,"KK_WITHDRAW")+SUMIFS(G:G,H:H,"BANK",D:D,"COMM_WITHDRAW")+SUMIFS(G:G,H:H,"BANK",D:D,"PROFIT_WITHDRAW")+SUMIFS(G:G,H:H,"BANK",D:D,"PAID")+SUMIFS(G:G,H:H,"BANK",D:D,"MISC")+SUMIFS(G:G,H:H,"BANK",D:D,"OTHER")+SUMIFS(G:G,H:H,"BANK",D:D,"MHN_PERSONAL")+SUMIFS(G:G,H:H,"BANK",D:D,"ADJUSTED")+SUMIFS(G:G,H:H,"BANK",D:D,"PROFIT_TO_CAP")+SUMIFS(G:G,H:H,"UPI",D:D,"PAYMENT")+SUMIFS(G:G,H:H,"UPI",D:D,"MOTOR")+SUMIFS(G:G,H:H,"UPI",D:D,"BHUSSA")+SUMIFS(G:G,H:H,"UPI",D:D,"GAWALI")+SUMIFS(G:G,H:H,"UPI",D:D,"CASH_ADV")+SUMIFS(G:G,H:H,"UPI",D:D,"DISCOUNT")+SUMIFS(G:G,H:H,"UPI",D:D,"WITHDRAWN")+SUMIFS(G:G,H:H,"UPI",D:D,"REPAID")+SUMIFS(G:G,H:H,"UPI",D:D,"GIVEN")+SUMIFS(G:G,H:H,"UPI",D:D,"MANDI")+SUMIFS(G:G,H:H,"UPI",D:D,"TRAVEL")+SUMIFS(G:G,H:H,"UPI",D:D,"FOOD")+SUMIFS(G:G,H:H,"UPI",D:D,"SALARY")+SUMIFS(G:G,H:H,"UPI",D:D,"BF_DISC")+SUMIFS(G:G,H:H,"UPI",D:D,"JB_PAID")+SUMIFS(G:G,H:H,"UPI",D:D,"JB_WITHDRAW")+SUMIFS(G:G,H:H,"UPI",D:D,"KK_WITHDRAW")+SUMIFS(G:G,H:H,"UPI",D:D,"COMM_WITHDRAW")+SUMIFS(G:G,H:H,"UPI",D:D,"PROFIT_WITHDRAW")+SUMIFS(G:G,H:H,"UPI",D:D,"PAID")+SUMIFS(G:G,H:H,"UPI",D:D,"MISC")+SUMIFS(G:G,H:H,"UPI",D:D,"OTHER")+SUMIFS(G:G,H:H,"UPI",D:D,"MHN_PERSONAL")+SUMIFS(G:G,H:H,"UPI",D:D,"ADJUSTED")+SUMIFS(G:G,H:H,"UPI",D:D,"PROFIT_TO_CAP")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"PAYMENT")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"MOTOR")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"BHUSSA")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"GAWALI")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"CASH_ADV")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"DISCOUNT")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"WITHDRAWN")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"REPAID")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"GIVEN")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"MANDI")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"TRAVEL")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"FOOD")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"SALARY")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"BF_DISC")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"JB_PAID")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"JB_WITHDRAW")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"KK_WITHDRAW")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"COMM_WITHDRAW")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"PROFIT_WITHDRAW")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"PAID")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"MISC")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"OTHER")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"MHN_PERSONAL")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"ADJUSTED")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"PROFIT_TO_CAP")</f>
+        <f>SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"PAYMENT")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"MOTOR")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"BHUSSA")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"GAWALI")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"CASH_ADV")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"DISCOUNT")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"WITHDRAWN")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"REPAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"GIVEN")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"MANDI")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"TRAVEL")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"FOOD")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"SALARY")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"BF_DISC")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"JB_PAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"JB_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"KK_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"COMM_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"PROFIT_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"PAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"MISC")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"OTHER")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"MHN_PERSONAL")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"ADJUSTED")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"PROFIT_TO_CAP")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"PAYMENT")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"MOTOR")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"BHUSSA")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"GAWALI")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"CASH_ADV")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"DISCOUNT")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"WITHDRAWN")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"REPAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"GIVEN")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"MANDI")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"TRAVEL")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"FOOD")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"SALARY")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"BF_DISC")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"JB_PAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"JB_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"KK_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"COMM_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"PROFIT_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"PAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"MISC")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"OTHER")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"MHN_PERSONAL")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"ADJUSTED")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"PROFIT_TO_CAP")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"PAYMENT")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"MOTOR")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"BHUSSA")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"GAWALI")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"CASH_ADV")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"DISCOUNT")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"WITHDRAWN")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"REPAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"GIVEN")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"MANDI")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"TRAVEL")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"FOOD")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"SALARY")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"BF_DISC")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"JB_PAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"JB_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"KK_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"COMM_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"PROFIT_WITHDRAW")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"PAID")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"MISC")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"OTHER")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"MHN_PERSONAL")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"ADJUSTED")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"PROFIT_TO_CAP")</f>
         <v/>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>SUMIFS(G:G,H:H,"CASH",D:D,"RECEIPT")+SUMIFS(G:G,H:H,"CASH",D:D,"TAKEN")+SUMIFS(G:G,H:H,"CASH",D:D,"RECEIVED")+SUMIFS(G:G,H:H,"CASH",D:D,"PROVISION")</f>
+        <f>SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"RECEIPT")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"TAKEN")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"RECEIVED")+SUMIFS(G$4:G$1003,H$4:H$1003,"CASH",D$4:D$1003,"PROVISION")</f>
         <v/>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="J8" s="12">
-        <f>SUMIFS(G:G,H:H,"BANK",D:D,"RECEIPT")+SUMIFS(G:G,H:H,"BANK",D:D,"TAKEN")+SUMIFS(G:G,H:H,"BANK",D:D,"RECEIVED")+SUMIFS(G:G,H:H,"BANK",D:D,"PROVISION")+SUMIFS(G:G,H:H,"UPI",D:D,"RECEIPT")+SUMIFS(G:G,H:H,"UPI",D:D,"TAKEN")+SUMIFS(G:G,H:H,"UPI",D:D,"RECEIVED")+SUMIFS(G:G,H:H,"UPI",D:D,"PROVISION")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"RECEIPT")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"TAKEN")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"RECEIVED")+SUMIFS(G:G,H:H,"TRANSFER",D:D,"PROVISION")</f>
+        <f>SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"RECEIPT")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"TAKEN")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"RECEIVED")+SUMIFS(G$4:G$1003,H$4:H$1003,"BANK",D$4:D$1003,"PROVISION")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"RECEIPT")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"TAKEN")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"RECEIVED")+SUMIFS(G$4:G$1003,H$4:H$1003,"UPI",D$4:D$1003,"PROVISION")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"RECEIPT")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"TAKEN")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"RECEIVED")+SUMIFS(G$4:G$1003,H$4:H$1003,"TRANSFER",D$4:D$1003,"PROVISION")</f>
         <v/>
       </c>
     </row>

--- a/frontend/public/Mandi_Master_V10.xlsx
+++ b/frontend/public/Mandi_Master_V10.xlsx
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B14" s="12">
-        <f>IF(B14&lt;&gt;"",B14*B8,B9*B13/100)</f>
+        <f>IF(B13&lt;&gt;"",B13*B7,B8*B12/100)</f>
         <v/>
       </c>
     </row>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="B15" s="12">
-        <f>IF(B8&gt;0,Masters!$Y$3,0)</f>
+        <f>IF(B7&gt;0,Masters!$Y$3,0)</f>
         <v/>
       </c>
     </row>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>B8*Masters!$Y$4</f>
+        <f>B7*Masters!$Y$4</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B21" s="13">
-        <f>SUM(B15:B21)</f>
+        <f>SUM(B14:B20)</f>
         <v/>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B24" s="12">
-        <f>B9</f>
+        <f>B8</f>
         <v/>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>B22</f>
+        <f>B21</f>
         <v/>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="B27" s="13">
-        <f>B25-B26+B27</f>
+        <f>B24-B25+B26</f>
         <v/>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B33" s="13">
-        <f>B28-B31+B32</f>
+        <f>B27-B30+B31</f>
         <v/>
       </c>
     </row>
